--- a/bindings/excel/examples/swap_pricing_example.xlsx
+++ b/bindings/excel/examples/swap_pricing_example.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="125">
   <si>
     <t>QuantSupport: SOFR and ESTR Curve Construction</t>
   </si>
@@ -302,10 +302,10 @@
     <t>Bootstraps the configured curves</t>
   </si>
   <si>
-    <t>4. Swap trade</t>
-  </si>
-  <si>
-    <t>Receive-fixed USD SOFR swap</t>
+    <t>4. Swap position</t>
+  </si>
+  <si>
+    <t>Position on instrument B15</t>
   </si>
   <si>
     <t>5. Present value</t>
@@ -317,7 +317,7 @@
     <t>6. Fair fixed rate</t>
   </si>
   <si>
-    <t>Par coupon implied by the curve</t>
+    <t>FairRate(0): fixed leg</t>
   </si>
   <si>
     <t>7. SOFR curve</t>
@@ -344,6 +344,27 @@
     <t>ESTR discount factor at maturity</t>
   </si>
   <si>
+    <t>Native swap contract</t>
+  </si>
+  <si>
+    <t>Explicit CSA policy</t>
+  </si>
+  <si>
+    <t>Native cashflow pricer</t>
+  </si>
+  <si>
+    <t>Requested native results</t>
+  </si>
+  <si>
+    <t>Cashflows</t>
+  </si>
+  <si>
+    <t>Sensitivities</t>
+  </si>
+  <si>
+    <t>Fair floating spread</t>
+  </si>
+  <si>
     <t>Bootstrapped SOFR and ESTR discount curves</t>
   </si>
   <si>
@@ -384,12 +405,6 @@
   </si>
   <si>
     <t>Swap outputs</t>
-  </si>
-  <si>
-    <t>Cashflows</t>
-  </si>
-  <si>
-    <t>Sensitivities</t>
   </si>
   <si>
     <t>Live worksheet-function help</t>
@@ -1481,16 +1496,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="58.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="40.7109375" style="1" customWidth="1"/>
-    <col min="4" max="14" width="18.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="14" width="18.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28" customHeight="1">
+    <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>76</v>
       </c>
@@ -1498,7 +1515,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
         <v>77</v>
       </c>
@@ -1509,7 +1526,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>80</v>
       </c>
@@ -1521,7 +1538,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>82</v>
       </c>
@@ -1533,7 +1550,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>84</v>
       </c>
@@ -1545,43 +1562,43 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B7" s="1" cm="1">
-        <f t="array" ref="B7">_xll.QS.TRADE.SWAP("SwapExample.Swap",'Curve Setup'!B3,'Trade Inputs'!B6,'Trade Inputs'!B7,'Trade Inputs'!B8,'Trade Inputs'!B9,'Trade Inputs'!B4,'Trade Inputs'!B5,0,'Trade Inputs'!B10,'Trade Inputs'!B11,'Trade Inputs'!B12,'Trade Inputs'!B13,'Trade Inputs'!B14,'Trade Inputs'!B15)</f>
+        <f t="array" ref="B7">_xll.QS.TRADE.CREATE("SwapExample.Swap",B15,'Curve Setup'!B3,'Trade Inputs'!B10)</f>
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B8" s="8" cm="1">
-        <f t="array" ref="B8">_xll.QS.PRICE(B7,B6)</f>
+        <f t="array" ref="B8">_xll.QS.RESULT.VALUE(B18)</f>
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="9" cm="1">
-        <f t="array" ref="B9">_xll.QS.FAIR.RATE(B7,B6)</f>
+        <f t="array" ref="B9">_xll.QS.RESULT.FAIR.RATE(B18)</f>
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>92</v>
       </c>
@@ -1593,7 +1610,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>94</v>
       </c>
@@ -1605,7 +1622,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>96</v>
       </c>
@@ -1617,7 +1634,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>98</v>
       </c>
@@ -1627,6 +1644,74 @@
       </c>
       <c r="C13" s="1" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="1" cm="1">
+        <f t="array" ref="B15">_xll.QS.INSTRUMENT.SWAP("SwapExample.Instrument",'Trade Inputs'!B6,'Trade Inputs'!B7,'Trade Inputs'!B8,'Trade Inputs'!B9,'Trade Inputs'!B4,'Trade Inputs'!B5,0,'Trade Inputs'!B11,'Trade Inputs'!B12,'Trade Inputs'!B13,'Trade Inputs'!B14,'Trade Inputs'!B15)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="1" cm="1">
+        <f t="array" ref="B16">_xll.QS.DISCOUNT.POLICY.CSA("SwapExample.Policy","USD","SOFR")</f>
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="1" cm="1">
+        <f t="array" ref="B17">_xll.QS.PRICER.CREATE("SwapExample.Pricer","DiscountedCashflowPricer",B16)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="1" cm="1">
+        <f t="array" ref="B18">_xll.QS.EVALUATE("SwapExample.Results",B17,B7,B6,E15:E18)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" cm="1">
+        <f t="array" ref="E18">_xll.QS.REQUEST.FAIR.RATE(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="1" cm="1">
+        <f t="array" ref="B20">_xll.QS.EVALUATE("SwapExample.FloatFair",B17,B7,B6,E20)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" cm="1">
+        <f t="array" ref="E20">_xll.QS.REQUEST.FAIR.RATE(1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="B21" s="1" cm="1">
+        <f t="array" ref="B21">_xll.QS.RESULT.FAIR.RATE(B20)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1658,7 +1743,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1676,21 +1761,21 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -1704,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="N4" s="1">
         <f>Pricing!B10</f>
@@ -1713,7 +1798,7 @@
     </row>
     <row r="5" spans="1:14">
       <c r="M5" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="N5" s="1">
         <f>'Trade Inputs'!B7</f>
@@ -1722,7 +1807,7 @@
     </row>
     <row r="6" spans="1:14">
       <c r="M6" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="N6" s="10" cm="1">
         <f t="array" ref="N6">_xll.QS.CURVE.DISCOUNT(Pricing!B10,N5)</f>
@@ -1731,7 +1816,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="M7" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N7" s="1">
         <f>Pricing!B12</f>
@@ -1740,7 +1825,7 @@
     </row>
     <row r="8" spans="1:14">
       <c r="M8" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="N8" s="10" cm="1">
         <f t="array" ref="N8">_xll.QS.CURVE.DISCOUNT(Pricing!B12,N5)</f>
@@ -1749,7 +1834,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="M9" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="N9" s="1">
         <f>'Trade Inputs'!B6</f>
@@ -1758,7 +1843,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="M10" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="N10" s="1">
         <f>'Trade Inputs'!B7</f>
@@ -1767,7 +1852,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="M11" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="N11" s="9" cm="1">
         <f t="array" ref="N11">_xll.QS.CURVE.FORWARD(Pricing!B10,N9,N10,"Simple","Annual")</f>
@@ -1776,7 +1861,7 @@
     </row>
     <row r="12" spans="1:14">
       <c r="M12" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="N12" s="9" cm="1">
         <f t="array" ref="N12">_xll.QS.CURVE.FORWARD(Pricing!B12,N9,N10,"Simple","Annual")</f>
@@ -1804,7 +1889,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1820,7 +1905,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1831,17 +1916,17 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="K3" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" cm="1">
-        <f t="array" ref="A4">_xll.QS.CASHFLOWS(Pricing!B7,Pricing!B6)</f>
+        <f t="array" ref="A4">_xll.QS.RESULT.CASHFLOWS(Pricing!B18)</f>
         <v>0</v>
       </c>
       <c r="K4" s="1" cm="1">
-        <f t="array" ref="K4">_xll.QS.SENSITIVITIES(Pricing!B7,Pricing!B6)</f>
+        <f t="array" ref="K4">_xll.QS.RESULT.SENSITIVITIES(Pricing!B18)</f>
         <v>0</v>
       </c>
     </row>
@@ -1873,7 +1958,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1885,15 +1970,15 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -1903,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" cm="1">
-        <f t="array" ref="D4">_xll.QS.HELP("QS.TRADE.SWAP")</f>
+        <f t="array" ref="D4">_xll.QS.HELP("QS.INSTRUMENT.SWAP")</f>
         <v>0</v>
       </c>
       <c r="G4" s="1" cm="1">

--- a/bindings/excel/examples/swap_pricing_example.xlsx
+++ b/bindings/excel/examples/swap_pricing_example.xlsx
@@ -28,14 +28,15 @@
     <definedName name="Swap_Compounding">'1 Inputs'!$B$17</definedName>
     <definedName name="Swap_Context">'3 Build'!$B$7</definedName>
     <definedName name="Swap_Currency">'1 Inputs'!$B$13</definedName>
-    <definedName name="Swap_Curves">'2 Market'!$B$106</definedName>
     <definedName name="Swap_DayCounter">'1 Inputs'!$B$16</definedName>
-    <definedName name="Swap_EstrCurve">'3 Build'!$B$40</definedName>
+    <definedName name="Swap_EstrConfig">'2 Market'!$B$109</definedName>
+    <definedName name="Swap_EstrContext">'3 Build'!$B$10</definedName>
+    <definedName name="Swap_EstrCurve">'3 Build'!$B$43</definedName>
     <definedName name="Swap_EstrDiscount">'4 Results'!$B$14</definedName>
     <definedName name="Swap_EstrForward">'4 Results'!$B$16</definedName>
     <definedName name="Swap_EstrQuotes">'2 Market'!$A$18:$A$30</definedName>
-    <definedName name="Swap_Fair0">'3 Build'!$B$28</definedName>
-    <definedName name="Swap_Fair1">'3 Build'!$B$34</definedName>
+    <definedName name="Swap_Fair0">'3 Build'!$B$31</definedName>
+    <definedName name="Swap_Fair1">'3 Build'!$B$37</definedName>
     <definedName name="Swap_FairFixed">'4 Results'!$B$8</definedName>
     <definedName name="Swap_FairFloat">'4 Results'!$B$9</definedName>
     <definedName name="Swap_FixedFrequency">'1 Inputs'!$B$19</definedName>
@@ -43,12 +44,13 @@
     <definedName name="Swap_FloatFrequency">'1 Inputs'!$B$20</definedName>
     <definedName name="Swap_Index">'1 Inputs'!$B$14</definedName>
     <definedName name="Swap_InitialCurves">'2 Market'!$B$100</definedName>
+    <definedName name="Swap_InitialEstrCurves">'2 Market'!$B$106</definedName>
     <definedName name="Swap_InitialQuotes">'2 Market'!$B$34</definedName>
-    <definedName name="Swap_Instrument">'3 Build'!$B$10</definedName>
+    <definedName name="Swap_Instrument">'3 Build'!$B$13</definedName>
     <definedName name="Swap_Maturity">'1 Inputs'!$B$12</definedName>
     <definedName name="Swap_Notional">'1 Inputs'!$B$8</definedName>
-    <definedName name="Swap_Policy">'3 Build'!$B$16</definedName>
-    <definedName name="Swap_Pricer">'3 Build'!$B$19</definedName>
+    <definedName name="Swap_Policy">'3 Build'!$B$19</definedName>
+    <definedName name="Swap_Pricer">'3 Build'!$B$22</definedName>
     <definedName name="Swap_PV">'4 Results'!$B$7</definedName>
     <definedName name="Swap_Quote10">'2 Market'!$B$64</definedName>
     <definedName name="Swap_Quote11">'2 Market'!$B$67</definedName>
@@ -73,19 +75,19 @@
     <definedName name="Swap_Quote9">'2 Market'!$B$61</definedName>
     <definedName name="Swap_Quotes">Swap_Quote21</definedName>
     <definedName name="Swap_RateFrequency">'1 Inputs'!$B$18</definedName>
-    <definedName name="Swap_Request0">'3 Build'!$B$25</definedName>
-    <definedName name="Swap_Request1">'3 Build'!$B$31</definedName>
+    <definedName name="Swap_Request0">'3 Build'!$B$28</definedName>
+    <definedName name="Swap_Request1">'3 Build'!$B$34</definedName>
     <definedName name="Swap_Requests">'1 Inputs'!$A$24:$A$26</definedName>
-    <definedName name="Swap_Result">'3 Build'!$B$22</definedName>
+    <definedName name="Swap_Result">'3 Build'!$B$25</definedName>
     <definedName name="Swap_Side">'1 Inputs'!$B$15</definedName>
     <definedName name="Swap_SofrConfig">'2 Market'!$B$103</definedName>
-    <definedName name="Swap_SofrCurve">'3 Build'!$B$37</definedName>
+    <definedName name="Swap_SofrCurve">'3 Build'!$B$40</definedName>
     <definedName name="Swap_SofrDiscount">'4 Results'!$B$13</definedName>
     <definedName name="Swap_SofrForward">'4 Results'!$B$15</definedName>
     <definedName name="Swap_SofrQuotes">'2 Market'!$A$7:$A$14</definedName>
     <definedName name="Swap_Spread">'1 Inputs'!$B$10</definedName>
     <definedName name="Swap_Start">'1 Inputs'!$B$11</definedName>
-    <definedName name="Swap_Trade">'3 Build'!$B$13</definedName>
+    <definedName name="Swap_Trade">'3 Build'!$B$16</definedName>
     <definedName name="Swap_ValuationDate">'1 Inputs'!$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -185,7 +187,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Use a currency consistent with the selected market index.</t>
+          <t>This study prices a USD contract in the USD/SOFR context.</t>
         </r>
       </text>
     </comment>
@@ -198,7 +200,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>SOFR and ESTR are constructed on the Market tab.</t>
+          <t>SOFR projects this swap; ESTR has a separate comparison context.</t>
         </r>
       </text>
     </comment>
@@ -585,7 +587,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Use Actual360 / LogLinear / extrapolation for both curves.</t>
+          <t>USD/SOFR and EUR/ESTR use separate bootstrap collateral assumptions.</t>
         </r>
       </text>
     </comment>
@@ -611,7 +613,20 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Adds EUR without replacing the USD configuration.</t>
+          <t>An independent configuration collection for the EUR/ESTR context.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B109" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>EUR OIS quotes bootstrap under EUR/ESTR collateral in their own context.</t>
         </r>
       </text>
     </comment>
@@ -634,7 +649,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Builds the curves configured on Market.</t>
+          <t>Bootstraps SOFR under USD collateral; this context prices the swap.</t>
         </r>
       </text>
     </comment>
@@ -647,11 +662,24 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t>Bootstraps ESTR under EUR collateral for comparison only.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t>The contract contains dates, rates and indices.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -664,7 +692,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0">
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -677,7 +705,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0">
+    <comment ref="B22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -690,7 +718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0">
+    <comment ref="B25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -703,7 +731,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B25" authorId="0">
+    <comment ref="B28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -716,7 +744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B28" authorId="0">
+    <comment ref="B31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -729,7 +757,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B31" authorId="0">
+    <comment ref="B34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -742,7 +770,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B34" authorId="0">
+    <comment ref="B37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -755,19 +783,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="B37" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Reusable curve object for point queries and node reports.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="B40" authorId="0">
       <text>
         <r>
@@ -777,7 +792,20 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Reusable curve object for point queries and node reports.</t>
+          <t>Reads the curve from its matching collateral context.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Reads the curve from its matching collateral context.</t>
         </r>
       </text>
     </comment>
@@ -909,12 +937,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="210">
   <si>
     <t>Swap pricing · a guided example</t>
   </si>
   <si>
-    <t>Build USD SOFR and EUR ESTR curves, then value one receive-fixed USD swap.</t>
+    <t>Value one receive-fixed USD swap under USD/SOFR collateral. Build a separate EUR/ESTR market for curve comparisons.</t>
   </si>
   <si>
     <t>Before you start: load quantsupport.xll in 64-bit Windows Excel, then press Ctrl+Alt+F9. Results are blank until Excel calculates. Dates are ISO text; enter 4% as 0.04.</t>
@@ -1091,7 +1119,7 @@
     <t>USD</t>
   </si>
   <si>
-    <t>Use a currency consistent with the selected market index.</t>
+    <t>This study prices a USD contract in the USD/SOFR context.</t>
   </si>
   <si>
     <t>Projection index</t>
@@ -1100,7 +1128,7 @@
     <t>SOFR</t>
   </si>
   <si>
-    <t>SOFR and ESTR are constructed on the Market tab.</t>
+    <t>SOFR projects this swap; ESTR has a separate comparison context.</t>
   </si>
   <si>
     <t>Position side</t>
@@ -1334,10 +1362,10 @@
     <t>2.21 Load quote</t>
   </si>
   <si>
-    <t>3. Create curve configurations</t>
-  </si>
-  <si>
-    <t>Use Actual360 / LogLinear / extrapolation for both curves.</t>
+    <t>3. Create USD configurations</t>
+  </si>
+  <si>
+    <t>USD/SOFR and EUR/ESTR use separate bootstrap collateral assumptions.</t>
   </si>
   <si>
     <t>4. Configure SOFR</t>
@@ -1346,10 +1374,16 @@
     <t>Bootstraps the visible USD deposit / OIS quotes.</t>
   </si>
   <si>
-    <t>5. Configure ESTR</t>
-  </si>
-  <si>
-    <t>Adds EUR without replacing the USD configuration.</t>
+    <t>5. Create EUR configurations</t>
+  </si>
+  <si>
+    <t>An independent configuration collection for the EUR/ESTR context.</t>
+  </si>
+  <si>
+    <t>6. Configure ESTR</t>
+  </si>
+  <si>
+    <t>EUR OIS quotes bootstrap under EUR/ESTR collateral in their own context.</t>
   </si>
   <si>
     <t>Build the pricing objects</t>
@@ -1367,10 +1401,16 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>1. Initialize the context</t>
-  </si>
-  <si>
-    <t>Builds the curves configured on Market.</t>
+    <t>1.1 Initialize USD context</t>
+  </si>
+  <si>
+    <t>Bootstraps SOFR under USD collateral; this context prices the swap.</t>
+  </si>
+  <si>
+    <t>1.2 Initialize EUR context</t>
+  </si>
+  <si>
+    <t>Bootstraps ESTR under EUR collateral for comparison only.</t>
   </si>
   <si>
     <t>2. Define the instrument</t>
@@ -1427,7 +1467,7 @@
     <t>9. Inspect SOFR</t>
   </si>
   <si>
-    <t>Reusable curve object for point queries and node reports.</t>
+    <t>Reads the curve from its matching collateral context.</t>
   </si>
   <si>
     <t>9. Inspect ESTR</t>
@@ -2510,7 +2550,7 @@
       <c r="A13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -2521,7 +2561,7 @@
       <c r="A14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -2651,7 +2691,7 @@
     <tabColor rgb="FF337AB7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="42.7109375" style="1" customWidth="1"/>
@@ -3324,7 +3364,7 @@
         <v>141</v>
       </c>
       <c r="B100" s="10" cm="1" t="str">
-        <f t="array" ref="B100">_xll.QS.CURVE.CONFIGS.CREATE("Swap.Curves")</f>
+        <f t="array" ref="B100">_xll.QS.CURVE.CONFIGS.CREATE("Swap.UsdCurves")</f>
         <v/>
       </c>
       <c r="C100" s="7" t="s">
@@ -3334,7 +3374,7 @@
     <row r="101" spans="1:3" ht="34" customHeight="1">
       <c r="A101" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B100),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.CREATE("Swap.Curves")</v>
+        <v>=QS.CURVE.CONFIGS.CREATE("Swap.UsdCurves")</v>
       </c>
       <c r="B101" s="13"/>
       <c r="C101" s="13"/>
@@ -3364,7 +3404,7 @@
         <v>145</v>
       </c>
       <c r="B106" s="10" cm="1" t="str">
-        <f t="array" ref="B106">_xll.QS.CURVE.CONFIGS.ADD(Swap_SofrConfig,"ESTR","Actual360","LogLinear",TRUE,Swap_EstrQuotes)</f>
+        <f t="array" ref="B106">_xll.QS.CURVE.CONFIGS.CREATE("Swap.EurCurves")</f>
         <v/>
       </c>
       <c r="C106" s="7" t="s">
@@ -3374,13 +3414,33 @@
     <row r="107" spans="1:3" ht="34" customHeight="1">
       <c r="A107" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B106),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.ADD(Swap_SofrConfig, "ESTR", "Actual360", "LogLinear", TRUE, Swap_EstrQuotes)</v>
+        <v>=QS.CURVE.CONFIGS.CREATE("Swap.EurCurves")</v>
       </c>
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
     </row>
+    <row r="109" spans="1:3" ht="38" customHeight="1">
+      <c r="A109" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B109" s="10" cm="1" t="str">
+        <f t="array" ref="B109">_xll.QS.CURVE.CONFIGS.ADD(Swap_InitialEstrCurves,"ESTR","Actual360","LogLinear",TRUE,Swap_EstrQuotes)</f>
+        <v/>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="34" customHeight="1">
+      <c r="A110" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B109),",",", ")</f>
+        <v>=QS.CURVE.CONFIGS.ADD(Swap_InitialEstrCurves, "ESTR", "Actual360", "LogLinear", TRUE, Swap_EstrQuotes)</v>
+      </c>
+      <c r="B110" s="13"/>
+      <c r="C110" s="13"/>
+    </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C3"/>
     <mergeCell ref="A35:C35"/>
@@ -3408,6 +3468,7 @@
     <mergeCell ref="A101:C101"/>
     <mergeCell ref="A104:C104"/>
     <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A110:C110"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
@@ -3428,7 +3489,7 @@
     <tabColor rgb="FF78909C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
@@ -3437,14 +3498,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3459,262 +3520,282 @@
         <v>39</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>116</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="38" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B7" s="10" cm="1" t="str">
-        <f t="array" ref="B7">_xll.QS.CONTEXT.CREATE("Swap.Context",Swap_Quotes,Swap_Curves,,,,,,,,,,Swap_Currency,Swap_Index,"Mid")</f>
+        <f t="array" ref="B7">_xll.QS.CONTEXT.CREATE("Swap.Context",Swap_Quotes,Swap_SofrConfig,,,,,,,,,,Swap_Currency,Swap_Index,"Mid")</f>
         <v/>
       </c>
       <c r="C7" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
-        <v>=QS.CONTEXT.CREATE("Swap.Context", Swap_Quotes, Swap_Curves, , , , , , , , , , Swap_Currency, Swap_Index, "Mid")</v>
+        <v>=QS.CONTEXT.CREATE("Swap.Context", Swap_Quotes, Swap_SofrConfig, , , , , , , , , , Swap_Currency, Swap_Index, "Mid")</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
     </row>
     <row r="10" spans="1:3" ht="38" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B10" s="10" cm="1" t="str">
-        <f t="array" ref="B10">_xll.QS.INSTRUMENT.SWAP("Swap.Instrument",Swap_Start,Swap_Maturity,Swap_Currency,Swap_Index,Swap_Notional,Swap_FixedRate,Swap_Spread,Swap_DayCounter,Swap_Compounding,Swap_RateFrequency,Swap_FixedFrequency,Swap_FloatFrequency)</f>
+        <f t="array" ref="B10">_xll.QS.CONTEXT.CREATE("Swap.EstrContext",Swap_Quotes,Swap_EstrConfig,,,,,,,,,,"EUR","ESTR","Mid")</f>
         <v/>
       </c>
       <c r="C10" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="48" customHeight="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
-        <v>=QS.INSTRUMENT.SWAP("Swap.Instrument", Swap_Start, Swap_Maturity, Swap_Currency, Swap_Index, Swap_Notional, Swap_FixedRate, Swap_Spread, Swap_DayCounter, Swap_Compounding, Swap_RateFrequency, Swap_FixedFrequency, Swap_FloatFrequency)</v>
+        <v>=QS.CONTEXT.CREATE("Swap.EstrContext", Swap_Quotes, Swap_EstrConfig, , , , , , , , , , "EUR", "ESTR", "Mid")</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
     </row>
     <row r="13" spans="1:3" ht="38" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B13" s="10" cm="1" t="str">
-        <f t="array" ref="B13">_xll.QS.TRADE.CREATE("Swap.Trade",Swap_Instrument,Swap_ValuationDate,Swap_Side)</f>
+        <f t="array" ref="B13">_xll.QS.INSTRUMENT.SWAP("Swap.Instrument",Swap_Start,Swap_Maturity,Swap_Currency,Swap_Index,Swap_Notional,Swap_FixedRate,Swap_Spread,Swap_DayCounter,Swap_Compounding,Swap_RateFrequency,Swap_FixedFrequency,Swap_FloatFrequency)</f>
         <v/>
       </c>
       <c r="C13" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="34" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="48" customHeight="1">
       <c r="A14" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Swap.Trade", Swap_Instrument, Swap_ValuationDate, Swap_Side)</v>
+        <v>=QS.INSTRUMENT.SWAP("Swap.Instrument", Swap_Start, Swap_Maturity, Swap_Currency, Swap_Index, Swap_Notional, Swap_FixedRate, Swap_Spread, Swap_DayCounter, Swap_Compounding, Swap_RateFrequency, Swap_FixedFrequency, Swap_FloatFrequency)</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
     </row>
     <row r="16" spans="1:3" ht="38" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B16" s="10" cm="1" t="str">
-        <f t="array" ref="B16">_xll.QS.DISCOUNT.POLICY.CSA("Swap.Policy",Swap_Currency,Swap_Index)</f>
+        <f t="array" ref="B16">_xll.QS.TRADE.CREATE("Swap.Trade",Swap_Instrument,Swap_ValuationDate,Swap_Side)</f>
         <v/>
       </c>
       <c r="C16" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="34" customHeight="1">
       <c r="A17" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
-        <v>=QS.DISCOUNT.POLICY.CSA("Swap.Policy", Swap_Currency, Swap_Index)</v>
+        <v>=QS.TRADE.CREATE("Swap.Trade", Swap_Instrument, Swap_ValuationDate, Swap_Side)</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
     </row>
     <row r="19" spans="1:3" ht="38" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B19" s="10" cm="1" t="str">
-        <f t="array" ref="B19">_xll.QS.PRICER.CREATE("Swap.Pricer","DiscountedCashflowPricer",Swap_Policy)</f>
+        <f t="array" ref="B19">_xll.QS.DISCOUNT.POLICY.CSA("Swap.Policy",Swap_Currency,Swap_Index)</f>
         <v/>
       </c>
       <c r="C19" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="34" customHeight="1">
       <c r="A20" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
-        <v>=QS.PRICER.CREATE("Swap.Pricer", "DiscountedCashflowPricer", Swap_Policy)</v>
+        <v>=QS.DISCOUNT.POLICY.CSA("Swap.Policy", Swap_Currency, Swap_Index)</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
     </row>
     <row r="22" spans="1:3" ht="38" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B22" s="10" cm="1" t="str">
-        <f t="array" ref="B22">_xll.QS.EVALUATE("Swap.Results",Swap_Pricer,Swap_Trade,Swap_Context,Swap_Requests)</f>
+        <f t="array" ref="B22">_xll.QS.PRICER.CREATE("Swap.Pricer","DiscountedCashflowPricer",Swap_Policy)</f>
         <v/>
       </c>
       <c r="C22" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="34" customHeight="1">
       <c r="A23" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
-        <v>=QS.EVALUATE("Swap.Results", Swap_Pricer, Swap_Trade, Swap_Context, Swap_Requests)</v>
+        <v>=QS.PRICER.CREATE("Swap.Pricer", "DiscountedCashflowPricer", Swap_Policy)</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
     </row>
     <row r="25" spans="1:3" ht="38" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B25" s="10" cm="1" t="str">
-        <f t="array" ref="B25">_xll.QS.REQUEST.FAIR.RATE(0)</f>
+        <f t="array" ref="B25">_xll.QS.EVALUATE("Swap.Results",Swap_Pricer,Swap_Trade,Swap_Context,Swap_Requests)</f>
         <v/>
       </c>
       <c r="C25" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="34" customHeight="1">
       <c r="A26" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
-        <v>=QS.REQUEST.FAIR.RATE(0)</v>
+        <v>=QS.EVALUATE("Swap.Results", Swap_Pricer, Swap_Trade, Swap_Context, Swap_Requests)</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
     </row>
     <row r="28" spans="1:3" ht="38" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B28" s="10" cm="1" t="str">
-        <f t="array" ref="B28">_xll.QS.EVALUATE("Swap.Fair0",Swap_Pricer,Swap_Trade,Swap_Context,Swap_Request0)</f>
+        <f t="array" ref="B28">_xll.QS.REQUEST.FAIR.RATE(0)</f>
         <v/>
       </c>
       <c r="C28" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="34" customHeight="1">
       <c r="A29" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
-        <v>=QS.EVALUATE("Swap.Fair0", Swap_Pricer, Swap_Trade, Swap_Context, Swap_Request0)</v>
+        <v>=QS.REQUEST.FAIR.RATE(0)</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
     </row>
     <row r="31" spans="1:3" ht="38" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B31" s="10" cm="1" t="str">
-        <f t="array" ref="B31">_xll.QS.REQUEST.FAIR.RATE(1)</f>
+        <f t="array" ref="B31">_xll.QS.EVALUATE("Swap.Fair0",Swap_Pricer,Swap_Trade,Swap_Context,Swap_Request0)</f>
         <v/>
       </c>
       <c r="C31" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="34" customHeight="1">
       <c r="A32" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
-        <v>=QS.REQUEST.FAIR.RATE(1)</v>
+        <v>=QS.EVALUATE("Swap.Fair0", Swap_Pricer, Swap_Trade, Swap_Context, Swap_Request0)</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
     </row>
     <row r="34" spans="1:3" ht="38" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B34" s="10" cm="1" t="str">
-        <f t="array" ref="B34">_xll.QS.EVALUATE("Swap.Fair1",Swap_Pricer,Swap_Trade,Swap_Context,Swap_Request1)</f>
+        <f t="array" ref="B34">_xll.QS.REQUEST.FAIR.RATE(1)</f>
         <v/>
       </c>
       <c r="C34" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="34" customHeight="1">
       <c r="A35" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B34),",",", ")</f>
-        <v>=QS.EVALUATE("Swap.Fair1", Swap_Pricer, Swap_Trade, Swap_Context, Swap_Request1)</v>
+        <v>=QS.REQUEST.FAIR.RATE(1)</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
     </row>
     <row r="37" spans="1:3" ht="38" customHeight="1">
       <c r="A37" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" s="10" cm="1" t="str">
+        <f t="array" ref="B37">_xll.QS.EVALUATE("Swap.Fair1",Swap_Pricer,Swap_Trade,Swap_Context,Swap_Request1)</f>
+        <v/>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="B37" s="10" cm="1" t="str">
-        <f t="array" ref="B37">_xll.QS.CURVE.GET(Swap_Context,"SOFR")</f>
-        <v/>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="34" customHeight="1">
       <c r="A38" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B37),",",", ")</f>
-        <v>=QS.CURVE.GET(Swap_Context, "SOFR")</v>
+        <v>=QS.EVALUATE("Swap.Fair1", Swap_Pricer, Swap_Trade, Swap_Context, Swap_Request1)</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
     </row>
     <row r="40" spans="1:3" ht="38" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B40" s="10" cm="1" t="str">
-        <f t="array" ref="B40">_xll.QS.CURVE.GET(Swap_Context,"ESTR")</f>
+        <f t="array" ref="B40">_xll.QS.CURVE.GET(Swap_Context,"SOFR")</f>
         <v/>
       </c>
       <c r="C40" s="7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="34" customHeight="1">
       <c r="A41" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B40),",",", ")</f>
-        <v>=QS.CURVE.GET(Swap_Context, "ESTR")</v>
+        <v>=QS.CURVE.GET(Swap_Context, "SOFR")</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
     </row>
+    <row r="43" spans="1:3" ht="38" customHeight="1">
+      <c r="A43" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B43" s="10" cm="1" t="str">
+        <f t="array" ref="B43">_xll.QS.CURVE.GET(Swap_EstrContext,"ESTR")</f>
+        <v/>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="34" customHeight="1">
+      <c r="A44" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B43),",",", ")</f>
+        <v>=QS.CURVE.GET(Swap_EstrContext, "ESTR")</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C3"/>
     <mergeCell ref="A8:C8"/>
@@ -3729,6 +3810,7 @@
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A44:C44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
@@ -3759,14 +3841,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3781,118 +3863,118 @@
         <v>39</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="34" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B7" s="14" cm="1" t="str">
         <f t="array" ref="B7">_xll.QS.RESULT.VALUE(Swap_Result)</f>
         <v/>
       </c>
       <c r="C7" s="7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B8" s="15" cm="1" t="str">
         <f t="array" ref="B8">_xll.QS.RESULT.FAIR.RATE(Swap_Fair0)</f>
         <v/>
       </c>
       <c r="C8" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="34" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B9" s="15" cm="1" t="str">
         <f t="array" ref="B9">_xll.QS.RESULT.FAIR.RATE(Swap_Fair1)</f>
         <v/>
       </c>
       <c r="C9" s="7" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="36" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="34" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B13" s="16" cm="1" t="str">
         <f t="array" ref="B13">_xll.QS.CURVE.DISCOUNT(Swap_SofrCurve,Swap_Maturity)</f>
         <v/>
       </c>
       <c r="C13" s="7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="34" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B14" s="16" cm="1" t="str">
         <f t="array" ref="B14">_xll.QS.CURVE.DISCOUNT(Swap_EstrCurve,Swap_Maturity)</f>
         <v/>
       </c>
       <c r="C14" s="7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="34" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B15" s="15" cm="1" t="str">
         <f t="array" ref="B15">_xll.QS.CURVE.FORWARD(Swap_SofrCurve,Swap_Start,Swap_Maturity,"Simple","Annual")</f>
         <v/>
       </c>
       <c r="C15" s="7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="34" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B16" s="15" cm="1" t="str">
         <f t="array" ref="B16">_xll.QS.CURVE.FORWARD(Swap_EstrCurve,Swap_Start,Swap_Maturity,"Simple","Annual")</f>
         <v/>
       </c>
       <c r="C16" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="24" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3935,7 +4017,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3948,7 +4030,7 @@
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3975,7 +4057,7 @@
         <v>39</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="24" customHeight="1">
@@ -4017,14 +4099,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4039,7 +4121,7 @@
         <v>39</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1">
@@ -4082,7 +4164,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4091,7 +4173,7 @@
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4112,7 +4194,7 @@
     </row>
     <row r="6" spans="1:5" ht="24" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -4127,7 +4209,7 @@
     </row>
     <row r="26" spans="1:5" ht="24" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>

--- a/bindings/excel/examples/swap_pricing_example.xlsx
+++ b/bindings/excel/examples/swap_pricing_example.xlsx
@@ -3539,7 +3539,7 @@
         <v>154</v>
       </c>
       <c r="B7" s="10" cm="1" t="str">
-        <f t="array" ref="B7">_xll.QS.CONTEXT.CREATE("Swap.Context",Swap_Quotes,Swap_SofrConfig,,,,,,,,,,Swap_Currency,Swap_Index,"Mid")</f>
+        <f t="array" ref="B7">_xll.QS.CONTEXT.FROM.COMPONENTS("Swap.Context",Swap_Quotes,Swap_SofrConfig,,,,,,,,,,Swap_Currency,Swap_Index,"Mid")</f>
         <v/>
       </c>
       <c r="C7" s="7" t="s">
@@ -3549,7 +3549,7 @@
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
-        <v>=QS.CONTEXT.CREATE("Swap.Context", Swap_Quotes, Swap_SofrConfig, , , , , , , , , , Swap_Currency, Swap_Index, "Mid")</v>
+        <v>=QS.CONTEXT.FROM.COMPONENTS("Swap.Context", Swap_Quotes, Swap_SofrConfig, , , , , , , , , , Swap_Currency, Swap_Index, "Mid")</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -3559,7 +3559,7 @@
         <v>156</v>
       </c>
       <c r="B10" s="10" cm="1" t="str">
-        <f t="array" ref="B10">_xll.QS.CONTEXT.CREATE("Swap.EstrContext",Swap_Quotes,Swap_EstrConfig,,,,,,,,,,"EUR","ESTR","Mid")</f>
+        <f t="array" ref="B10">_xll.QS.CONTEXT.FROM.COMPONENTS("Swap.EstrContext",Swap_Quotes,Swap_EstrConfig,,,,,,,,,,"EUR","ESTR","Mid")</f>
         <v/>
       </c>
       <c r="C10" s="7" t="s">
@@ -3569,7 +3569,7 @@
     <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
-        <v>=QS.CONTEXT.CREATE("Swap.EstrContext", Swap_Quotes, Swap_EstrConfig, , , , , , , , , , "EUR", "ESTR", "Mid")</v>
+        <v>=QS.CONTEXT.FROM.COMPONENTS("Swap.EstrContext", Swap_Quotes, Swap_EstrConfig, , , , , , , , , , "EUR", "ESTR", "Mid")</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>

--- a/bindings/excel/examples/swap_pricing_example.xlsx
+++ b/bindings/excel/examples/swap_pricing_example.xlsx
@@ -29,12 +29,14 @@
     <definedName name="Swap_Context">'3 Build'!$B$7</definedName>
     <definedName name="Swap_Currency">'1 Inputs'!$B$13</definedName>
     <definedName name="Swap_DayCounter">'1 Inputs'!$B$16</definedName>
-    <definedName name="Swap_EstrConfig">'2 Market'!$B$109</definedName>
     <definedName name="Swap_EstrContext">'3 Build'!$B$10</definedName>
     <definedName name="Swap_EstrCurve">'3 Build'!$B$43</definedName>
     <definedName name="Swap_EstrDiscount">'4 Results'!$B$14</definedName>
     <definedName name="Swap_EstrForward">'4 Results'!$B$16</definedName>
     <definedName name="Swap_EstrQuotes">'2 Market'!$A$18:$A$30</definedName>
+    <definedName name="Swap_EurInputs">'2 Market'!$B$43</definedName>
+    <definedName name="Swap_EurMid">'2 Market'!$B$18:$B$30</definedName>
+    <definedName name="Swap_EurRoot">'2 Market'!$B$40</definedName>
     <definedName name="Swap_Fair0">'3 Build'!$B$31</definedName>
     <definedName name="Swap_Fair1">'3 Build'!$B$37</definedName>
     <definedName name="Swap_FairFixed">'4 Results'!$B$8</definedName>
@@ -43,44 +45,18 @@
     <definedName name="Swap_FixedRate">'1 Inputs'!$B$9</definedName>
     <definedName name="Swap_FloatFrequency">'1 Inputs'!$B$20</definedName>
     <definedName name="Swap_Index">'1 Inputs'!$B$14</definedName>
-    <definedName name="Swap_InitialCurves">'2 Market'!$B$100</definedName>
-    <definedName name="Swap_InitialEstrCurves">'2 Market'!$B$106</definedName>
-    <definedName name="Swap_InitialQuotes">'2 Market'!$B$34</definedName>
     <definedName name="Swap_Instrument">'3 Build'!$B$13</definedName>
     <definedName name="Swap_Maturity">'1 Inputs'!$B$12</definedName>
     <definedName name="Swap_Notional">'1 Inputs'!$B$8</definedName>
     <definedName name="Swap_Policy">'3 Build'!$B$19</definedName>
     <definedName name="Swap_Pricer">'3 Build'!$B$22</definedName>
     <definedName name="Swap_PV">'4 Results'!$B$7</definedName>
-    <definedName name="Swap_Quote10">'2 Market'!$B$64</definedName>
-    <definedName name="Swap_Quote11">'2 Market'!$B$67</definedName>
-    <definedName name="Swap_Quote12">'2 Market'!$B$70</definedName>
-    <definedName name="Swap_Quote13">'2 Market'!$B$73</definedName>
-    <definedName name="Swap_Quote14">'2 Market'!$B$76</definedName>
-    <definedName name="Swap_Quote15">'2 Market'!$B$79</definedName>
-    <definedName name="Swap_Quote16">'2 Market'!$B$82</definedName>
-    <definedName name="Swap_Quote17">'2 Market'!$B$85</definedName>
-    <definedName name="Swap_Quote18">'2 Market'!$B$88</definedName>
-    <definedName name="Swap_Quote19">'2 Market'!$B$91</definedName>
-    <definedName name="Swap_Quote1">'2 Market'!$B$37</definedName>
-    <definedName name="Swap_Quote20">'2 Market'!$B$94</definedName>
-    <definedName name="Swap_Quote21">'2 Market'!$B$97</definedName>
-    <definedName name="Swap_Quote2">'2 Market'!$B$40</definedName>
-    <definedName name="Swap_Quote3">'2 Market'!$B$43</definedName>
-    <definedName name="Swap_Quote4">'2 Market'!$B$46</definedName>
-    <definedName name="Swap_Quote5">'2 Market'!$B$49</definedName>
-    <definedName name="Swap_Quote6">'2 Market'!$B$52</definedName>
-    <definedName name="Swap_Quote7">'2 Market'!$B$55</definedName>
-    <definedName name="Swap_Quote8">'2 Market'!$B$58</definedName>
-    <definedName name="Swap_Quote9">'2 Market'!$B$61</definedName>
-    <definedName name="Swap_Quotes">Swap_Quote21</definedName>
     <definedName name="Swap_RateFrequency">'1 Inputs'!$B$18</definedName>
     <definedName name="Swap_Request0">'3 Build'!$B$28</definedName>
     <definedName name="Swap_Request1">'3 Build'!$B$34</definedName>
     <definedName name="Swap_Requests">'1 Inputs'!$A$24:$A$26</definedName>
     <definedName name="Swap_Result">'3 Build'!$B$25</definedName>
     <definedName name="Swap_Side">'1 Inputs'!$B$15</definedName>
-    <definedName name="Swap_SofrConfig">'2 Market'!$B$103</definedName>
     <definedName name="Swap_SofrCurve">'3 Build'!$B$40</definedName>
     <definedName name="Swap_SofrDiscount">'4 Results'!$B$13</definedName>
     <definedName name="Swap_SofrForward">'4 Results'!$B$15</definedName>
@@ -88,6 +64,9 @@
     <definedName name="Swap_Spread">'1 Inputs'!$B$10</definedName>
     <definedName name="Swap_Start">'1 Inputs'!$B$11</definedName>
     <definedName name="Swap_Trade">'3 Build'!$B$16</definedName>
+    <definedName name="Swap_UsdInputs">'2 Market'!$B$37</definedName>
+    <definedName name="Swap_UsdMid">'2 Market'!$B$7:$B$14</definedName>
+    <definedName name="Swap_UsdRoot">'2 Market'!$B$34</definedName>
     <definedName name="Swap_ValuationDate">'1 Inputs'!$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -301,7 +280,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>All quotes share this valuation date.</t>
+          <t>Context owns its stores and conventions.</t>
         </r>
       </text>
     </comment>
@@ -314,7 +293,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Updates form one ordered store chain.</t>
+          <t>Independent quote identifiers and levels; no quote-store chain.</t>
         </r>
       </text>
     </comment>
@@ -327,7 +306,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Updates form one ordered store chain.</t>
+          <t>Context owns its stores and conventions.</t>
         </r>
       </text>
     </comment>
@@ -340,293 +319,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B46" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B49" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B52" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B55" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B58" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B61" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B64" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B67" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B70" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B73" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B76" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B79" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B82" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B85" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B88" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B91" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B94" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B97" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Updates form one ordered store chain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B100" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>USD/SOFR and EUR/ESTR use separate bootstrap collateral assumptions.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B103" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Bootstraps the visible USD deposit / OIS quotes.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B106" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>An independent configuration collection for the EUR/ESTR context.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B109" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>EUR OIS quotes bootstrap under EUR/ESTR collateral in their own context.</t>
+          <t>Independent quote identifiers and levels; no quote-store chain.</t>
         </r>
       </text>
     </comment>
@@ -937,7 +630,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="184">
   <si>
     <t>Swap pricing · a guided example</t>
   </si>
@@ -1290,100 +983,22 @@
     <t>Object reference</t>
   </si>
   <si>
-    <t>1. Create quote store</t>
-  </si>
-  <si>
-    <t>All quotes share this valuation date.</t>
-  </si>
-  <si>
-    <t>2.1 Load quote</t>
-  </si>
-  <si>
-    <t>Updates form one ordered store chain.</t>
-  </si>
-  <si>
-    <t>2.2 Load quote</t>
-  </si>
-  <si>
-    <t>2.3 Load quote</t>
-  </si>
-  <si>
-    <t>2.4 Load quote</t>
-  </si>
-  <si>
-    <t>2.5 Load quote</t>
-  </si>
-  <si>
-    <t>2.6 Load quote</t>
-  </si>
-  <si>
-    <t>2.7 Load quote</t>
-  </si>
-  <si>
-    <t>2.8 Load quote</t>
-  </si>
-  <si>
-    <t>2.9 Load quote</t>
-  </si>
-  <si>
-    <t>2.10 Load quote</t>
-  </si>
-  <si>
-    <t>2.11 Load quote</t>
-  </si>
-  <si>
-    <t>2.12 Load quote</t>
-  </si>
-  <si>
-    <t>2.13 Load quote</t>
-  </si>
-  <si>
-    <t>2.14 Load quote</t>
-  </si>
-  <si>
-    <t>2.15 Load quote</t>
-  </si>
-  <si>
-    <t>2.16 Load quote</t>
-  </si>
-  <si>
-    <t>2.17 Load quote</t>
-  </si>
-  <si>
-    <t>2.18 Load quote</t>
-  </si>
-  <si>
-    <t>2.19 Load quote</t>
-  </si>
-  <si>
-    <t>2.20 Load quote</t>
-  </si>
-  <si>
-    <t>2.21 Load quote</t>
-  </si>
-  <si>
-    <t>3. Create USD configurations</t>
-  </si>
-  <si>
-    <t>USD/SOFR and EUR/ESTR use separate bootstrap collateral assumptions.</t>
-  </si>
-  <si>
-    <t>4. Configure SOFR</t>
-  </si>
-  <si>
-    <t>Bootstraps the visible USD deposit / OIS quotes.</t>
-  </si>
-  <si>
-    <t>5. Create EUR configurations</t>
-  </si>
-  <si>
-    <t>An independent configuration collection for the EUR/ESTR context.</t>
-  </si>
-  <si>
-    <t>6. Configure ESTR</t>
-  </si>
-  <si>
-    <t>EUR OIS quotes bootstrap under EUR/ESTR collateral in their own context.</t>
+    <t>Create USD context</t>
+  </si>
+  <si>
+    <t>Context owns its stores and conventions.</t>
+  </si>
+  <si>
+    <t>Add SOFR curve and quotes</t>
+  </si>
+  <si>
+    <t>Independent quote identifiers and levels; no quote-store chain.</t>
+  </si>
+  <si>
+    <t>Create EUR context</t>
+  </si>
+  <si>
+    <t>Add ESTR curve and quotes</t>
   </si>
   <si>
     <t>Build the pricing objects</t>
@@ -2691,7 +2306,7 @@
     <tabColor rgb="FF337AB7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="42.7109375" style="1" customWidth="1"/>
@@ -2924,7 +2539,7 @@
         <v>117</v>
       </c>
       <c r="B34" s="10" cm="1" t="str">
-        <f t="array" ref="B34">_xll.QS.QUOTES.CREATE("Swap.Quotes",Swap_ValuationDate)</f>
+        <f t="array" ref="B34">_xll.QS.CONTEXT.CREATE("Swap.Usd",Swap_ValuationDate,"USD","SOFR")</f>
         <v/>
       </c>
       <c r="C34" s="7" t="s">
@@ -2934,7 +2549,7 @@
     <row r="35" spans="1:3" ht="34" customHeight="1">
       <c r="A35" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B34),",",", ")</f>
-        <v>=QS.QUOTES.CREATE("Swap.Quotes", Swap_ValuationDate)</v>
+        <v>=QS.CONTEXT.CREATE("Swap.Usd", Swap_ValuationDate, "USD", "SOFR")</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2944,7 +2559,7 @@
         <v>119</v>
       </c>
       <c r="B37" s="10" cm="1" t="str">
-        <f t="array" ref="B37">_xll.QS.QUOTES.SET(Swap_InitialQuotes,'2 Market'!A7,'2 Market'!B7,,)</f>
+        <f t="array" ref="B37">_xll.QS.CONTEXT.ADD.CURVE(Swap_UsdRoot,"SOFR",Swap_SofrQuotes,Swap_UsdMid,,,"Actual360","LogLinear",TRUE)</f>
         <v/>
       </c>
       <c r="C37" s="7" t="s">
@@ -2954,7 +2569,7 @@
     <row r="38" spans="1:3" ht="34" customHeight="1">
       <c r="A38" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B37),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_InitialQuotes, '2 Market'!A7, '2 Market'!B7, , )</v>
+        <v>=QS.CONTEXT.ADD.CURVE(Swap_UsdRoot, "SOFR", Swap_SofrQuotes, Swap_UsdMid, , , "Actual360", "LogLinear", TRUE)</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -2964,17 +2579,17 @@
         <v>121</v>
       </c>
       <c r="B40" s="10" cm="1" t="str">
-        <f t="array" ref="B40">_xll.QS.QUOTES.SET(Swap_Quote1,'2 Market'!A8,'2 Market'!B8,,)</f>
+        <f t="array" ref="B40">_xll.QS.CONTEXT.CREATE("Swap.Eur",Swap_ValuationDate,"EUR","ESTR")</f>
         <v/>
       </c>
       <c r="C40" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="34" customHeight="1">
       <c r="A41" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B40),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote1, '2 Market'!A8, '2 Market'!B8, , )</v>
+        <v>=QS.CONTEXT.CREATE("Swap.Eur", Swap_ValuationDate, "EUR", "ESTR")</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -2984,7 +2599,7 @@
         <v>122</v>
       </c>
       <c r="B43" s="10" cm="1" t="str">
-        <f t="array" ref="B43">_xll.QS.QUOTES.SET(Swap_Quote2,'2 Market'!A9,'2 Market'!B9,,)</f>
+        <f t="array" ref="B43">_xll.QS.CONTEXT.ADD.CURVE(Swap_EurRoot,"ESTR",Swap_EstrQuotes,Swap_EurMid,,,"Actual360","LogLinear",TRUE)</f>
         <v/>
       </c>
       <c r="C43" s="7" t="s">
@@ -2994,481 +2609,19 @@
     <row r="44" spans="1:3" ht="34" customHeight="1">
       <c r="A44" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B43),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote2, '2 Market'!A9, '2 Market'!B9, , )</v>
+        <v>=QS.CONTEXT.ADD.CURVE(Swap_EurRoot, "ESTR", Swap_EstrQuotes, Swap_EurMid, , , "Actual360", "LogLinear", TRUE)</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
     </row>
-    <row r="46" spans="1:3" ht="38" customHeight="1">
-      <c r="A46" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B46" s="10" cm="1" t="str">
-        <f t="array" ref="B46">_xll.QS.QUOTES.SET(Swap_Quote3,'2 Market'!A10,'2 Market'!B10,,)</f>
-        <v/>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="34" customHeight="1">
-      <c r="A47" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B46),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote3, '2 Market'!A10, '2 Market'!B10, , )</v>
-      </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-    </row>
-    <row r="49" spans="1:3" ht="38" customHeight="1">
-      <c r="A49" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B49" s="10" cm="1" t="str">
-        <f t="array" ref="B49">_xll.QS.QUOTES.SET(Swap_Quote4,'2 Market'!A11,'2 Market'!B11,,)</f>
-        <v/>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="34" customHeight="1">
-      <c r="A50" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B49),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote4, '2 Market'!A11, '2 Market'!B11, , )</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-    </row>
-    <row r="52" spans="1:3" ht="38" customHeight="1">
-      <c r="A52" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B52" s="10" cm="1" t="str">
-        <f t="array" ref="B52">_xll.QS.QUOTES.SET(Swap_Quote5,'2 Market'!A12,'2 Market'!B12,,)</f>
-        <v/>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="34" customHeight="1">
-      <c r="A53" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B52),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote5, '2 Market'!A12, '2 Market'!B12, , )</v>
-      </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-    </row>
-    <row r="55" spans="1:3" ht="38" customHeight="1">
-      <c r="A55" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B55" s="10" cm="1" t="str">
-        <f t="array" ref="B55">_xll.QS.QUOTES.SET(Swap_Quote6,'2 Market'!A13,'2 Market'!B13,,)</f>
-        <v/>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="34" customHeight="1">
-      <c r="A56" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B55),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote6, '2 Market'!A13, '2 Market'!B13, , )</v>
-      </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-    </row>
-    <row r="58" spans="1:3" ht="38" customHeight="1">
-      <c r="A58" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B58" s="10" cm="1" t="str">
-        <f t="array" ref="B58">_xll.QS.QUOTES.SET(Swap_Quote7,'2 Market'!A14,'2 Market'!B14,,)</f>
-        <v/>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="34" customHeight="1">
-      <c r="A59" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B58),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote7, '2 Market'!A14, '2 Market'!B14, , )</v>
-      </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-    </row>
-    <row r="61" spans="1:3" ht="38" customHeight="1">
-      <c r="A61" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B61" s="10" cm="1" t="str">
-        <f t="array" ref="B61">_xll.QS.QUOTES.SET(Swap_Quote8,'2 Market'!A18,'2 Market'!B18,,)</f>
-        <v/>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="34" customHeight="1">
-      <c r="A62" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B61),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote8, '2 Market'!A18, '2 Market'!B18, , )</v>
-      </c>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-    </row>
-    <row r="64" spans="1:3" ht="38" customHeight="1">
-      <c r="A64" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B64" s="10" cm="1" t="str">
-        <f t="array" ref="B64">_xll.QS.QUOTES.SET(Swap_Quote9,'2 Market'!A19,'2 Market'!B19,,)</f>
-        <v/>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="34" customHeight="1">
-      <c r="A65" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B64),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote9, '2 Market'!A19, '2 Market'!B19, , )</v>
-      </c>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-    </row>
-    <row r="67" spans="1:3" ht="38" customHeight="1">
-      <c r="A67" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B67" s="10" cm="1" t="str">
-        <f t="array" ref="B67">_xll.QS.QUOTES.SET(Swap_Quote10,'2 Market'!A20,'2 Market'!B20,,)</f>
-        <v/>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="34" customHeight="1">
-      <c r="A68" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B67),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote10, '2 Market'!A20, '2 Market'!B20, , )</v>
-      </c>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-    </row>
-    <row r="70" spans="1:3" ht="38" customHeight="1">
-      <c r="A70" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B70" s="10" cm="1" t="str">
-        <f t="array" ref="B70">_xll.QS.QUOTES.SET(Swap_Quote11,'2 Market'!A21,'2 Market'!B21,,)</f>
-        <v/>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="34" customHeight="1">
-      <c r="A71" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B70),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote11, '2 Market'!A21, '2 Market'!B21, , )</v>
-      </c>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-    </row>
-    <row r="73" spans="1:3" ht="38" customHeight="1">
-      <c r="A73" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B73" s="10" cm="1" t="str">
-        <f t="array" ref="B73">_xll.QS.QUOTES.SET(Swap_Quote12,'2 Market'!A22,'2 Market'!B22,,)</f>
-        <v/>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="34" customHeight="1">
-      <c r="A74" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B73),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote12, '2 Market'!A22, '2 Market'!B22, , )</v>
-      </c>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-    </row>
-    <row r="76" spans="1:3" ht="38" customHeight="1">
-      <c r="A76" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B76" s="10" cm="1" t="str">
-        <f t="array" ref="B76">_xll.QS.QUOTES.SET(Swap_Quote13,'2 Market'!A23,'2 Market'!B23,,)</f>
-        <v/>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="34" customHeight="1">
-      <c r="A77" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B76),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote13, '2 Market'!A23, '2 Market'!B23, , )</v>
-      </c>
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
-    </row>
-    <row r="79" spans="1:3" ht="38" customHeight="1">
-      <c r="A79" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B79" s="10" cm="1" t="str">
-        <f t="array" ref="B79">_xll.QS.QUOTES.SET(Swap_Quote14,'2 Market'!A24,'2 Market'!B24,,)</f>
-        <v/>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="34" customHeight="1">
-      <c r="A80" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B79),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote14, '2 Market'!A24, '2 Market'!B24, , )</v>
-      </c>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13"/>
-    </row>
-    <row r="82" spans="1:3" ht="38" customHeight="1">
-      <c r="A82" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B82" s="10" cm="1" t="str">
-        <f t="array" ref="B82">_xll.QS.QUOTES.SET(Swap_Quote15,'2 Market'!A25,'2 Market'!B25,,)</f>
-        <v/>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="34" customHeight="1">
-      <c r="A83" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B82),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote15, '2 Market'!A25, '2 Market'!B25, , )</v>
-      </c>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13"/>
-    </row>
-    <row r="85" spans="1:3" ht="38" customHeight="1">
-      <c r="A85" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B85" s="10" cm="1" t="str">
-        <f t="array" ref="B85">_xll.QS.QUOTES.SET(Swap_Quote16,'2 Market'!A26,'2 Market'!B26,,)</f>
-        <v/>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="34" customHeight="1">
-      <c r="A86" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B85),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote16, '2 Market'!A26, '2 Market'!B26, , )</v>
-      </c>
-      <c r="B86" s="13"/>
-      <c r="C86" s="13"/>
-    </row>
-    <row r="88" spans="1:3" ht="38" customHeight="1">
-      <c r="A88" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B88" s="10" cm="1" t="str">
-        <f t="array" ref="B88">_xll.QS.QUOTES.SET(Swap_Quote17,'2 Market'!A27,'2 Market'!B27,,)</f>
-        <v/>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="34" customHeight="1">
-      <c r="A89" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B88),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote17, '2 Market'!A27, '2 Market'!B27, , )</v>
-      </c>
-      <c r="B89" s="13"/>
-      <c r="C89" s="13"/>
-    </row>
-    <row r="91" spans="1:3" ht="38" customHeight="1">
-      <c r="A91" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B91" s="10" cm="1" t="str">
-        <f t="array" ref="B91">_xll.QS.QUOTES.SET(Swap_Quote18,'2 Market'!A28,'2 Market'!B28,,)</f>
-        <v/>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="34" customHeight="1">
-      <c r="A92" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B91),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote18, '2 Market'!A28, '2 Market'!B28, , )</v>
-      </c>
-      <c r="B92" s="13"/>
-      <c r="C92" s="13"/>
-    </row>
-    <row r="94" spans="1:3" ht="38" customHeight="1">
-      <c r="A94" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B94" s="10" cm="1" t="str">
-        <f t="array" ref="B94">_xll.QS.QUOTES.SET(Swap_Quote19,'2 Market'!A29,'2 Market'!B29,,)</f>
-        <v/>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="34" customHeight="1">
-      <c r="A95" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B94),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote19, '2 Market'!A29, '2 Market'!B29, , )</v>
-      </c>
-      <c r="B95" s="13"/>
-      <c r="C95" s="13"/>
-    </row>
-    <row r="97" spans="1:3" ht="38" customHeight="1">
-      <c r="A97" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B97" s="10" cm="1" t="str">
-        <f t="array" ref="B97">_xll.QS.QUOTES.SET(Swap_Quote20,'2 Market'!A30,'2 Market'!B30,,)</f>
-        <v/>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="34" customHeight="1">
-      <c r="A98" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B97),",",", ")</f>
-        <v>=QS.QUOTES.SET(Swap_Quote20, '2 Market'!A30, '2 Market'!B30, , )</v>
-      </c>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13"/>
-    </row>
-    <row r="100" spans="1:3" ht="38" customHeight="1">
-      <c r="A100" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B100" s="10" cm="1" t="str">
-        <f t="array" ref="B100">_xll.QS.CURVE.CONFIGS.CREATE("Swap.UsdCurves")</f>
-        <v/>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="34" customHeight="1">
-      <c r="A101" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B100),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.CREATE("Swap.UsdCurves")</v>
-      </c>
-      <c r="B101" s="13"/>
-      <c r="C101" s="13"/>
-    </row>
-    <row r="103" spans="1:3" ht="38" customHeight="1">
-      <c r="A103" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B103" s="10" cm="1" t="str">
-        <f t="array" ref="B103">_xll.QS.CURVE.CONFIGS.ADD(Swap_InitialCurves,"SOFR","Actual360","LogLinear",TRUE,Swap_SofrQuotes)</f>
-        <v/>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="34" customHeight="1">
-      <c r="A104" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B103),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.ADD(Swap_InitialCurves, "SOFR", "Actual360", "LogLinear", TRUE, Swap_SofrQuotes)</v>
-      </c>
-      <c r="B104" s="13"/>
-      <c r="C104" s="13"/>
-    </row>
-    <row r="106" spans="1:3" ht="38" customHeight="1">
-      <c r="A106" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B106" s="10" cm="1" t="str">
-        <f t="array" ref="B106">_xll.QS.CURVE.CONFIGS.CREATE("Swap.EurCurves")</f>
-        <v/>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="34" customHeight="1">
-      <c r="A107" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B106),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.CREATE("Swap.EurCurves")</v>
-      </c>
-      <c r="B107" s="13"/>
-      <c r="C107" s="13"/>
-    </row>
-    <row r="109" spans="1:3" ht="38" customHeight="1">
-      <c r="A109" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B109" s="10" cm="1" t="str">
-        <f t="array" ref="B109">_xll.QS.CURVE.CONFIGS.ADD(Swap_InitialEstrCurves,"ESTR","Actual360","LogLinear",TRUE,Swap_EstrQuotes)</f>
-        <v/>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="34" customHeight="1">
-      <c r="A110" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B109),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.ADD(Swap_InitialEstrCurves, "ESTR", "Actual360", "LogLinear", TRUE, Swap_EstrQuotes)</v>
-      </c>
-      <c r="B110" s="13"/>
-      <c r="C110" s="13"/>
-    </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="6">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C3"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A110:C110"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
@@ -3498,14 +2651,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3520,70 +2673,70 @@
         <v>39</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>116</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="38" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="B7" s="10" cm="1" t="str">
-        <f t="array" ref="B7">_xll.QS.CONTEXT.FROM.COMPONENTS("Swap.Context",Swap_Quotes,Swap_SofrConfig,,,,,,,,,,Swap_Currency,Swap_Index,"Mid")</f>
+        <f t="array" ref="B7">_xll.QS.CONTEXT.PREPARE("Swap.Context",Swap_UsdRoot,Swap_UsdInputs)</f>
         <v/>
       </c>
       <c r="C7" s="7" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
-        <v>=QS.CONTEXT.FROM.COMPONENTS("Swap.Context", Swap_Quotes, Swap_SofrConfig, , , , , , , , , , Swap_Currency, Swap_Index, "Mid")</v>
+        <v>=QS.CONTEXT.PREPARE("Swap.Context", Swap_UsdRoot, Swap_UsdInputs)</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
     </row>
     <row r="10" spans="1:3" ht="38" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="B10" s="10" cm="1" t="str">
-        <f t="array" ref="B10">_xll.QS.CONTEXT.FROM.COMPONENTS("Swap.EstrContext",Swap_Quotes,Swap_EstrConfig,,,,,,,,,,"EUR","ESTR","Mid")</f>
+        <f t="array" ref="B10">_xll.QS.CONTEXT.PREPARE("Swap.EstrContext",Swap_EurRoot,Swap_EurInputs)</f>
         <v/>
       </c>
       <c r="C10" s="7" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
-        <v>=QS.CONTEXT.FROM.COMPONENTS("Swap.EstrContext", Swap_Quotes, Swap_EstrConfig, , , , , , , , , , "EUR", "ESTR", "Mid")</v>
+        <v>=QS.CONTEXT.PREPARE("Swap.EstrContext", Swap_EurRoot, Swap_EurInputs)</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
     </row>
     <row r="13" spans="1:3" ht="38" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="B13" s="10" cm="1" t="str">
         <f t="array" ref="B13">_xll.QS.INSTRUMENT.SWAP("Swap.Instrument",Swap_Start,Swap_Maturity,Swap_Currency,Swap_Index,Swap_Notional,Swap_FixedRate,Swap_Spread,Swap_DayCounter,Swap_Compounding,Swap_RateFrequency,Swap_FixedFrequency,Swap_FloatFrequency)</f>
         <v/>
       </c>
       <c r="C13" s="7" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="48" customHeight="1">
@@ -3596,14 +2749,14 @@
     </row>
     <row r="16" spans="1:3" ht="38" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="B16" s="10" cm="1" t="str">
         <f t="array" ref="B16">_xll.QS.TRADE.CREATE("Swap.Trade",Swap_Instrument,Swap_ValuationDate,Swap_Side)</f>
         <v/>
       </c>
       <c r="C16" s="7" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="34" customHeight="1">
@@ -3616,14 +2769,14 @@
     </row>
     <row r="19" spans="1:3" ht="38" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="B19" s="10" cm="1" t="str">
         <f t="array" ref="B19">_xll.QS.DISCOUNT.POLICY.CSA("Swap.Policy",Swap_Currency,Swap_Index)</f>
         <v/>
       </c>
       <c r="C19" s="7" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="34" customHeight="1">
@@ -3636,14 +2789,14 @@
     </row>
     <row r="22" spans="1:3" ht="38" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="B22" s="10" cm="1" t="str">
         <f t="array" ref="B22">_xll.QS.PRICER.CREATE("Swap.Pricer","DiscountedCashflowPricer",Swap_Policy)</f>
         <v/>
       </c>
       <c r="C22" s="7" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="34" customHeight="1">
@@ -3656,34 +2809,34 @@
     </row>
     <row r="25" spans="1:3" ht="38" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="B25" s="10" cm="1" t="str">
-        <f t="array" ref="B25">_xll.QS.EVALUATE("Swap.Results",Swap_Pricer,Swap_Trade,Swap_Context,Swap_Requests)</f>
+        <f t="array" ref="B25">_xll.QS.EVALUATE.RESULTS(Swap_Context,Swap_Trade,Swap_Requests,,Swap_Pricer)</f>
         <v/>
       </c>
       <c r="C25" s="7" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="34" customHeight="1">
       <c r="A26" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
-        <v>=QS.EVALUATE("Swap.Results", Swap_Pricer, Swap_Trade, Swap_Context, Swap_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Swap_Context, Swap_Trade, Swap_Requests, , Swap_Pricer)</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
     </row>
     <row r="28" spans="1:3" ht="38" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="B28" s="10" cm="1" t="str">
         <f t="array" ref="B28">_xll.QS.REQUEST.FAIR.RATE(0)</f>
         <v/>
       </c>
       <c r="C28" s="7" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="34" customHeight="1">
@@ -3696,34 +2849,34 @@
     </row>
     <row r="31" spans="1:3" ht="38" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="B31" s="10" cm="1" t="str">
-        <f t="array" ref="B31">_xll.QS.EVALUATE("Swap.Fair0",Swap_Pricer,Swap_Trade,Swap_Context,Swap_Request0)</f>
+        <f t="array" ref="B31">_xll.QS.EVALUATE.RESULTS(Swap_Context,Swap_Trade,Swap_Request0,,Swap_Pricer)</f>
         <v/>
       </c>
       <c r="C31" s="7" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="34" customHeight="1">
       <c r="A32" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
-        <v>=QS.EVALUATE("Swap.Fair0", Swap_Pricer, Swap_Trade, Swap_Context, Swap_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Swap_Context, Swap_Trade, Swap_Request0, , Swap_Pricer)</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
     </row>
     <row r="34" spans="1:3" ht="38" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B34" s="10" cm="1" t="str">
         <f t="array" ref="B34">_xll.QS.REQUEST.FAIR.RATE(1)</f>
         <v/>
       </c>
       <c r="C34" s="7" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="34" customHeight="1">
@@ -3736,34 +2889,34 @@
     </row>
     <row r="37" spans="1:3" ht="38" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="B37" s="10" cm="1" t="str">
-        <f t="array" ref="B37">_xll.QS.EVALUATE("Swap.Fair1",Swap_Pricer,Swap_Trade,Swap_Context,Swap_Request1)</f>
+        <f t="array" ref="B37">_xll.QS.EVALUATE.RESULTS(Swap_Context,Swap_Trade,Swap_Request1,,Swap_Pricer)</f>
         <v/>
       </c>
       <c r="C37" s="7" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="34" customHeight="1">
       <c r="A38" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B37),",",", ")</f>
-        <v>=QS.EVALUATE("Swap.Fair1", Swap_Pricer, Swap_Trade, Swap_Context, Swap_Request1)</v>
+        <v>=QS.EVALUATE.RESULTS(Swap_Context, Swap_Trade, Swap_Request1, , Swap_Pricer)</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
     </row>
     <row r="40" spans="1:3" ht="38" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="B40" s="10" cm="1" t="str">
         <f t="array" ref="B40">_xll.QS.CURVE.GET(Swap_Context,"SOFR")</f>
         <v/>
       </c>
       <c r="C40" s="7" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="34" customHeight="1">
@@ -3776,14 +2929,14 @@
     </row>
     <row r="43" spans="1:3" ht="38" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="B43" s="10" cm="1" t="str">
         <f t="array" ref="B43">_xll.QS.CURVE.GET(Swap_EstrContext,"ESTR")</f>
         <v/>
       </c>
       <c r="C43" s="7" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="34" customHeight="1">
@@ -3841,14 +2994,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3863,118 +3016,118 @@
         <v>39</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="34" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="B7" s="14" cm="1" t="str">
         <f t="array" ref="B7">_xll.QS.RESULT.VALUE(Swap_Result)</f>
         <v/>
       </c>
       <c r="C7" s="7" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="B8" s="15" cm="1" t="str">
         <f t="array" ref="B8">_xll.QS.RESULT.FAIR.RATE(Swap_Fair0)</f>
         <v/>
       </c>
       <c r="C8" s="7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="34" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="B9" s="15" cm="1" t="str">
         <f t="array" ref="B9">_xll.QS.RESULT.FAIR.RATE(Swap_Fair1)</f>
         <v/>
       </c>
       <c r="C9" s="7" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="36" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="34" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="B13" s="16" cm="1" t="str">
         <f t="array" ref="B13">_xll.QS.CURVE.DISCOUNT(Swap_SofrCurve,Swap_Maturity)</f>
         <v/>
       </c>
       <c r="C13" s="7" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="34" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="B14" s="16" cm="1" t="str">
         <f t="array" ref="B14">_xll.QS.CURVE.DISCOUNT(Swap_EstrCurve,Swap_Maturity)</f>
         <v/>
       </c>
       <c r="C14" s="7" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="34" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="B15" s="15" cm="1" t="str">
         <f t="array" ref="B15">_xll.QS.CURVE.FORWARD(Swap_SofrCurve,Swap_Start,Swap_Maturity,"Simple","Annual")</f>
         <v/>
       </c>
       <c r="C15" s="7" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="34" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="B16" s="15" cm="1" t="str">
         <f t="array" ref="B16">_xll.QS.CURVE.FORWARD(Swap_EstrCurve,Swap_Start,Swap_Maturity,"Simple","Annual")</f>
         <v/>
       </c>
       <c r="C16" s="7" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="24" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -4017,7 +3170,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4030,7 +3183,7 @@
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4057,7 +3210,7 @@
         <v>39</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="24" customHeight="1">
@@ -4099,14 +3252,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4121,7 +3274,7 @@
         <v>39</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1">
@@ -4164,7 +3317,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4173,7 +3326,7 @@
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4194,7 +3347,7 @@
     </row>
     <row r="6" spans="1:5" ht="24" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -4209,7 +3362,7 @@
     </row>
     <row r="26" spans="1:5" ht="24" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
